--- a/templates/product_keyword_templates.xlsx
+++ b/templates/product_keyword_templates.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产品关键词明细" sheetId="1" r:id="R2c14aa6b7a994b44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ASIN模板" sheetId="2" r:id="R853517e8f05040ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="关键词模板" sheetId="3" r:id="R4e7fd0c73d91490a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产品关键词明细" sheetId="1" r:id="R30feae2efb8e4d0b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ASIN模板" sheetId="2" r:id="R3021439c7204486c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="关键词模板" sheetId="3" r:id="R55d53187ac344784"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -276,41 +276,41 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
-        <x:v>SD3 Pivot Shower Door</x:v>
+        <x:v>Dog Crate Furniture Example</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>B0XXXXXXXXX</x:v>
+        <x:v>ASIN_PLACEHOLDER</x:v>
       </x:c>
       <x:c r="C2" t="str">
-        <x:v>pivot shower door</x:v>
+        <x:v>dog crate furniture</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
-        <x:v>SD3 Pivot Shower Door</x:v>
+        <x:v>Dog Crate Furniture Example</x:v>
       </x:c>
       <x:c r="B3" t="str">
-        <x:v>B0XXXXXXXXX</x:v>
+        <x:v>ASIN_PLACEHOLDER</x:v>
       </x:c>
       <x:c r="C3" t="str">
-        <x:v>38 inch shower door</x:v>
+        <x:v>wooden dog crate furniture</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str">
-        <x:v>Socket Fan Light</x:v>
+        <x:v>Dog Furniture Example</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>B0YYYYYYYYY</x:v>
+        <x:v>ASIN_PLACEHOLDER</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>socket fan light</x:v>
+        <x:v>dog furniture</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc16541e4f0ff4537"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re0ee8d8a787a4b57"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -333,18 +333,18 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
-        <x:v>SD3 Pivot Shower Door</x:v>
+        <x:v>Dog Crate Furniture Example</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>B0XXXXXXXXX</x:v>
+        <x:v>ASIN_PLACEHOLDER</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
-        <x:v>Socket Fan Light</x:v>
+        <x:v>Dog Furniture Example</x:v>
       </x:c>
       <x:c r="B3" t="str">
-        <x:v>B0YYYYYYYYY</x:v>
+        <x:v>ASIN_PLACEHOLDER</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -366,17 +366,27 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
-        <x:v>pivot shower door</x:v>
+        <x:v>dog crate furniture</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
-        <x:v>38 inch shower door</x:v>
+        <x:v>wooden dog crate furniture</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str">
-        <x:v>brushed nickel shower door</x:v>
+        <x:v>dog furniture</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>dog kennel furniture</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>large dog crate furniture</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
